--- a/DADOS EXTERNOS.xlsx
+++ b/DADOS EXTERNOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Samuel\Desktop\CONSULT\autobras\Indicadores Atb\FINANCEIRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5BE7079D-085D-47CE-8314-EFFD8025D3E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145368AB-AB72-4E1D-BF75-A330F3CE5350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{677CDEDD-A89D-4E35-B452-0764E7A83DD0}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7185" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7195" uniqueCount="123">
   <si>
     <t>ação social</t>
   </si>
@@ -382,6 +382,21 @@
   </si>
   <si>
     <t>RECEITA</t>
+  </si>
+  <si>
+    <t>ALMOÇO</t>
+  </si>
+  <si>
+    <t>Imobilizado de escritorio</t>
+  </si>
+  <si>
+    <t>Impostos - IPTU</t>
+  </si>
+  <si>
+    <t>Instalação fechadura</t>
+  </si>
+  <si>
+    <t>—</t>
   </si>
 </sst>
 </file>
@@ -826,7 +841,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE394A55-AB2B-44EE-B3DD-F68ADECBE364}">
-  <dimension ref="A1:B3552"/>
+  <dimension ref="A1:B3557"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="52" style="1" bestFit="1" customWidth="1"/>
@@ -29248,6 +29263,46 @@
       </c>
       <c r="B3552" s="12" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="3553" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3553" t="s">
+        <v>118</v>
+      </c>
+      <c r="B3553" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3554" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3554" t="s">
+        <v>119</v>
+      </c>
+      <c r="B3554" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3555" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3555" t="s">
+        <v>120</v>
+      </c>
+      <c r="B3555" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3556" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3556" t="s">
+        <v>121</v>
+      </c>
+      <c r="B3556" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3557" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3557" t="s">
+        <v>122</v>
+      </c>
+      <c r="B3557" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/DADOS EXTERNOS.xlsx
+++ b/DADOS EXTERNOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Samuel\Desktop\CONSULT\autobras\Indicadores Atb\FINANCEIRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145368AB-AB72-4E1D-BF75-A330F3CE5350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A52F285-53E9-4A5E-BBC3-A48A5D9F27EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{677CDEDD-A89D-4E35-B452-0764E7A83DD0}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7195" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7201" uniqueCount="126">
   <si>
     <t>ação social</t>
   </si>
@@ -397,6 +397,15 @@
   </si>
   <si>
     <t>—</t>
+  </si>
+  <si>
+    <t>Despesas bancárias</t>
+  </si>
+  <si>
+    <t>PRONAMPE</t>
+  </si>
+  <si>
+    <t>despesas</t>
   </si>
 </sst>
 </file>
@@ -841,7 +850,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE394A55-AB2B-44EE-B3DD-F68ADECBE364}">
-  <dimension ref="A1:B3557"/>
+  <dimension ref="A1:B3560"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="52" style="1" bestFit="1" customWidth="1"/>
@@ -29303,6 +29312,30 @@
       </c>
       <c r="B3557" t="s">
         <v>122</v>
+      </c>
+    </row>
+    <row r="3558" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3558" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3558" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3559" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3559" t="s">
+        <v>124</v>
+      </c>
+      <c r="B3559" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3560" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3560" t="s">
+        <v>125</v>
+      </c>
+      <c r="B3560" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/DADOS EXTERNOS.xlsx
+++ b/DADOS EXTERNOS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Samuel\Desktop\CONSULT\autobras\Indicadores Atb\FINANCEIRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A52F285-53E9-4A5E-BBC3-A48A5D9F27EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{387FD979-E97D-4329-8441-6BDEDCF6548A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{677CDEDD-A89D-4E35-B452-0764E7A83DD0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{677CDEDD-A89D-4E35-B452-0764E7A83DD0}"/>
   </bookViews>
   <sheets>
     <sheet name="TIPO" sheetId="5" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7201" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7203" uniqueCount="127">
   <si>
     <t>ação social</t>
   </si>
@@ -406,6 +406,9 @@
   </si>
   <si>
     <t>despesas</t>
+  </si>
+  <si>
+    <t>DESPESAS VIAGEM CHINA</t>
   </si>
 </sst>
 </file>
@@ -850,7 +853,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE394A55-AB2B-44EE-B3DD-F68ADECBE364}">
-  <dimension ref="A1:B3560"/>
+  <dimension ref="A1:B3561"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="52" style="1" bestFit="1" customWidth="1"/>
@@ -29335,6 +29338,14 @@
         <v>125</v>
       </c>
       <c r="B3560" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3561" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3561" t="s">
+        <v>126</v>
+      </c>
+      <c r="B3561" s="1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -29570,7 +29581,9 @@
       <c r="B20" s="4">
         <v>2026</v>
       </c>
-      <c r="C20" s="4"/>
+      <c r="C20" s="8">
+        <v>1389098.33</v>
+      </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
@@ -29848,7 +29861,9 @@
       <c r="B20" s="4">
         <v>2026</v>
       </c>
-      <c r="C20" s="4"/>
+      <c r="C20" s="8">
+        <v>905787.58</v>
+      </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
@@ -30131,7 +30146,10 @@
       <c r="B20" s="4">
         <v>2026</v>
       </c>
-      <c r="C20" s="3"/>
+      <c r="C20" s="3">
+        <f>837476.43+427033.63</f>
+        <v>1264510.06</v>
+      </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A21" s="4" t="s">
